--- a/data/trans_orig/P79A6_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79A6_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26979</t>
+          <t>32508</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>21486</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36293</t>
+          <t>40858</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>55581</t>
+          <t>68980</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>57258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64742</t>
+          <t>78198</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>29282</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33856</t>
+          <t>29982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>74058</t>
+          <t>87240</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74058</t>
+          <t>87240</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>74058</t>
+          <t>87240</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>18244</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>30394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33410</t>
+          <t>37378</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>29756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37938</t>
+          <t>41549</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>52980</t>
+          <t>62878</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44562</t>
+          <t>53336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59978</t>
+          <t>69118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13642</t>
+          <t>15114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>15107</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23525</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>68087</t>
+          <t>78948</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>68087</t>
+          <t>78948</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>68087</t>
+          <t>78948</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25726</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20088</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29005</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>35073</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22981</t>
+          <t>29211</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32792</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>54338</t>
+          <t>66157</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47349</t>
+          <t>58266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60218</t>
+          <t>72406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11194</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>12859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22722</t>
+          <t>26999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31282</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31282</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31282</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>46255</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>46255</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>46255</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>70071</t>
+          <t>85265</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>70071</t>
+          <t>85265</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70071</t>
+          <t>85265</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43005</t>
+          <t>49138</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>42580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46177</t>
+          <t>53337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46425</t>
+          <t>53587</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42130</t>
+          <t>48159</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49753</t>
+          <t>57081</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>89431</t>
+          <t>102725</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82251</t>
+          <t>95897</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94209</t>
+          <t>108228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19644</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48448</t>
+          <t>56419</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48448</t>
+          <t>56419</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48448</t>
+          <t>56419</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53446</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53446</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53446</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>101895</t>
+          <t>117934</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>101895</t>
+          <t>117934</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>101895</t>
+          <t>117934</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>51453</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40538</t>
+          <t>44225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50592</t>
+          <t>55627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>52676</t>
+          <t>60422</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48251</t>
+          <t>55370</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55484</t>
+          <t>63711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>99504</t>
+          <t>111874</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92265</t>
+          <t>103601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104375</t>
+          <t>117534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>16372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10228</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19584</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53370</t>
+          <t>60597</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53370</t>
+          <t>60597</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53370</t>
+          <t>60597</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>58479</t>
+          <t>67481</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58479</t>
+          <t>67481</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58479</t>
+          <t>67481</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>111849</t>
+          <t>128078</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>111849</t>
+          <t>128078</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>111849</t>
+          <t>128078</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30869</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33170</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33823</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30390</t>
+          <t>34457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35568</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>64693</t>
+          <t>72410</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60011</t>
+          <t>67109</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67556</t>
+          <t>75602</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34183</t>
+          <t>37820</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34183</t>
+          <t>37820</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34183</t>
+          <t>37820</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>41414</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>41414</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>41414</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>70877</t>
+          <t>79235</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>70877</t>
+          <t>79235</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>70877</t>
+          <t>79235</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>24333</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>35222</t>
+          <t>39686</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32407</t>
+          <t>37067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35983</t>
+          <t>40982</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>60631</t>
+          <t>67938</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56455</t>
+          <t>63537</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62169</t>
+          <t>69806</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>467</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>41449</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>41449</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>41449</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>62490</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>62490</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>62490</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>220010</t>
+          <t>256037</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>207996</t>
+          <t>242453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>229921</t>
+          <t>266812</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>257146</t>
+          <t>296924</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>238496</t>
+          <t>279280</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>270105</t>
+          <t>310830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>477156</t>
+          <t>552961</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>455883</t>
+          <t>533348</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>493374</t>
+          <t>569764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,0%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20360</t>
+          <t>26877</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>51236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>51899</t>
+          <t>56829</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>42923</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70549</t>
+          <t>74473</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>82170</t>
+          <t>94481</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65952</t>
+          <t>77678</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>114094</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
